--- a/data/kocaeli/service_status_grid.xlsx
+++ b/data/kocaeli/service_status_grid.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,12 +32,8 @@
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
-    <font>
-      <b val="1"/>
-      <sz val="14"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -56,24 +52,6 @@
         <bgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor rgb="FFFFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
-        <bgColor rgb="FF00B050"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor rgb="FFFF0000"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -87,21 +65,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -469,13 +438,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D91"/>
+  <dimension ref="A1:K91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
@@ -486,573 +462,503 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>KOC001</t>
+          <t>4119</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>KOC002</t>
+          <t>4120</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>KOC003</t>
+          <t>4121</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>4122</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>4123</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>4124</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>4125</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>4126</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>4127</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>4128</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46013</v>
+        <v>46028</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46014</v>
+        <v>46029</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46015</v>
+        <v>46030</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46016</v>
+        <v>46031</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46017</v>
+        <v>46032</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46018</v>
+        <v>46033</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46019</v>
+        <v>46034</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46020</v>
+        <v>46035</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46021</v>
+        <v>46036</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46022</v>
+        <v>46037</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>46023</v>
+        <v>46038</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46024</v>
+        <v>46039</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>46025</v>
+        <v>46040</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46026</v>
+        <v>46041</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>46027</v>
+        <v>46042</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>46028</v>
+        <v>46043</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>46029</v>
+        <v>46044</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>46030</v>
+        <v>46045</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>46031</v>
+        <v>46046</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>46032</v>
+        <v>46047</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>46033</v>
+        <v>46048</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>46034</v>
+        <v>46049</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>46035</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>46036</v>
+        <v>46051</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>46037</v>
+        <v>46052</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>46038</v>
+        <v>46053</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>46039</v>
+        <v>46054</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>46040</v>
+        <v>46055</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>46041</v>
+        <v>46056</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>46042</v>
+        <v>46057</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>46043</v>
+        <v>46058</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>46044</v>
+        <v>46059</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>46045</v>
+        <v>46060</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>46046</v>
+        <v>46061</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>46047</v>
+        <v>46062</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>46048</v>
+        <v>46063</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>46049</v>
+        <v>46064</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>46050</v>
+        <v>46065</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>46051</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>46052</v>
+        <v>46067</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>46053</v>
+        <v>46068</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>46054</v>
+        <v>46069</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>46055</v>
+        <v>46070</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>46056</v>
+        <v>46071</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>46057</v>
+        <v>46072</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>46058</v>
+        <v>46073</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>46059</v>
+        <v>46074</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>46060</v>
+        <v>46075</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>46061</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>46062</v>
+        <v>46077</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>46063</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>46064</v>
+        <v>46079</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>46065</v>
+        <v>46080</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>46066</v>
+        <v>46081</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>46067</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>46068</v>
+        <v>46083</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>46069</v>
+        <v>46084</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>46070</v>
+        <v>46085</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>46072</v>
+        <v>46087</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>46073</v>
+        <v>46088</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>46074</v>
+        <v>46089</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>46075</v>
+        <v>46090</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>46076</v>
+        <v>46091</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>46077</v>
+        <v>46092</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>46078</v>
+        <v>46093</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>46079</v>
+        <v>46094</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>46080</v>
+        <v>46095</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>46081</v>
+        <v>46096</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>46082</v>
+        <v>46097</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>46083</v>
+        <v>46098</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>46084</v>
+        <v>46099</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>46085</v>
+        <v>46100</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>46086</v>
+        <v>46101</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>46087</v>
+        <v>46102</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>46088</v>
+        <v>46103</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>46089</v>
+        <v>46104</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>46090</v>
+        <v>46105</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>46091</v>
+        <v>46106</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>46092</v>
+        <v>46107</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>46093</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>46094</v>
+        <v>46109</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>46095</v>
+        <v>46110</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>46096</v>
-      </c>
-      <c r="B85" s="3" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="C85" s="4" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="D85" s="4" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
+        <v>46111</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B86" s="3" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="C86" s="5" t="inlineStr">
-        <is>
-          <t>⚠</t>
-        </is>
-      </c>
-      <c r="D86" s="4" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
+        <v>46112</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>46098</v>
-      </c>
-      <c r="B87" s="4" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="C87" s="3" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D87" s="3" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>46113</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B88" s="3" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="C88" s="3" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D88" s="3" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>46114</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>46100</v>
-      </c>
-      <c r="B89" s="3" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="C89" s="4" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="D89" s="5" t="inlineStr">
-        <is>
-          <t>⚠</t>
-        </is>
+        <v>46115</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>46101</v>
-      </c>
-      <c r="B90" s="5" t="inlineStr">
-        <is>
-          <t>⚠</t>
-        </is>
-      </c>
-      <c r="C90" s="5" t="inlineStr">
-        <is>
-          <t>⚠</t>
-        </is>
-      </c>
-      <c r="D90" s="3" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>46116</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>46102</v>
-      </c>
-      <c r="B91" s="5" t="inlineStr">
-        <is>
-          <t>⚠</t>
-        </is>
-      </c>
-      <c r="C91" s="3" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D91" s="3" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>46117</v>
       </c>
     </row>
   </sheetData>
